--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
@@ -1923,6 +1923,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -2276,6 +2277,7 @@
       </c>
       <c r="G26" s="2" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -2429,7 +2431,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>**町・受託者**</t>
+          <t>町・受託者</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -2581,7 +2583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2735,12 +2737,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。未確定115箇所（協議会で設定54／町データ待ち43／決定後に記載12／見える化出力待ち6）</t>
+          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。9月29日に、調査結果報告書の原本との突合により認知症の設問の項目名（54.1％）を訂正した。未確定115箇所（協議会で設定54／町データ待ち43／決定後に記載12／見える化出力待ち6）</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2781,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。開催日が決まり次第お出しできます</t>
+          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。9月29日に、認知症の設問の項目名を素案と同じ内容に訂正した。開催日が決まり次第お出しできます</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2847,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2867,7 +2869,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2889,7 +2891,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2911,12 +2913,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>9月28日受領の令和8年度交付金 該当状況調査票集計表（市町村分）及び評価指標による。537点／800点・全国平均を82点上回る。適正化は強み。最大の弱点は在宅医療・在宅介護連携</t>
+          <t>9月28日受領の令和8年度交付金 該当状況調査票集計表（市町村分）及び評価指標による。537点／800点・全国平均を82点上回る。適正化は強み。最大の弱点は在宅医療・在宅介護連携。9月29日に、活動指標群の分析（入院時情報連携加算は上位1割で満点、退院・退所加算は上位7割にも入らず0点）を加えた</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2935,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>**9月28日**</t>
+          <t>9月28日</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>同上の計数編。指標別の得点・0点の項目・伸びしろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>小野町_令和7年度調査_集計結果・分析報告書_20260805.docx</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8月5日</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>9月29日に、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名を訂正した。報告書そのものの中の食い違い2件（回収数と集計の基数、通いの場の本文と図）は第4章に記載</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3065,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>**25分**</t>
+          <t>25分</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3063,7 +3087,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>**25分**</t>
+          <t>25分</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3080,7 +3104,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>交付金の取りまとめ</t>
+          <t>交付金の取りまとめと調査結果報告書の点検</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3090,7 +3114,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>537点／800点。適正化は強み。弱点は在宅医療・在宅介護連携</t>
+          <t>537点／800点。適正化は強み。弱点は在宅医療・在宅介護連携。調査結果報告書の原本を受領し、集計値を全件突き合わせました</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
@@ -2732,17 +2732,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第6版_20260928.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第7版_20260929.docx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9月28日</t>
+          <t>9月29日</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。9月29日に、調査結果報告書の原本との突合により認知症の設問の項目名（54.1％）を訂正した。未確定115箇所（協議会で設定54／町データ待ち43／決定後に記載12／見える化出力待ち6）</t>
+          <t>第7版。第6版（9月28日）で、第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加し、第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。第7版では、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名（54.1％）を訂正した。未確定115箇所（協議会で設定54／町データ待ち43／決定後に記載12／見える化出力待ち6）</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
@@ -2776,17 +2776,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小野町高齢者福祉サービス推進協議会資料_第9期計画の評価と令和7年度調査結果_20260928.docx</t>
+          <t>小野町高齢者福祉サービス推進協議会資料_第9期計画の評価と令和7年度調査結果_20260929.docx</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9月28日</t>
+          <t>9月29日</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。9月29日に、認知症の設問の項目名を素案と同じ内容に訂正した。開催日が決まり次第お出しできます</t>
+          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。第3版。9月29日に、調査結果報告書の原本との突合により認知症の設問の項目名を訂正し、報告書の食い違い3件を第2部に注記した。開催日が決まり次第お出しできます</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260929.xlsx
@@ -1060,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>見える化システム「要介護認定率」の県内比較の出力</t>
+          <t>見える化システム「要介護認定率」の県内順位の出力</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>成果品で「認定率は県内でも高い方にある」としている裏づけです。当方の手元にあるのは小野町の値（性・年齢調整後の地域差指数1.24）と令和7年3月末の県内2位までで、令和8年3月末の県内順位の出力がありません。見える化の地域別画面（B4系）の出力でお願いします</t>
+          <t>成果品で「認定率は県内でも高い方にある」としている裏づけです。9月30日にお送りいただいた地域分析・検討シートにより、県平均・全国平均との比較はできるようになりました（本町22.70％・県19.91％・全国20.32％）。残っているのは県内での順位です。見える化の地域別画面（B4系）の出力でお願いします</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>第2章3（全国・県内との比較）</t>
+          <t>第2章3（全国・県内との比較）、地域分析・検討シート</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -1634,6 +1634,62 @@
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>令和7年度調査の個票データ（提供が難しい場合はクロス集計表）</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>地域分析・検討シートで「在宅が伸びていない主因は利用に結びつかないこと」という仮説を立てました。その検証には、サービスを利用していない154人がどういう状態の方なのか（要介護度別・世帯構成別）が要ります。単純集計表からは作れません</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>地域分析・検討シート（受給率の検証方法）、計画素案 第2章2</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>訪問介護事業所の従事者数・受入可否・稼働率</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>訪問介護の受給者1人あたり給付月額が全国の52％、利用回数が50％と、在宅サービスの中で最も低くなっています。供給が足りないのか、ケアプランに組み込まれにくいのかで対応策が変わります。見える化の事業所別指標（令和8年7月の新機能）でも一部確かめられます</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>地域分析・検討シート（給付月額の検証方法）、計画素案 第2章5</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2583,7 +2639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2963,6 +3019,28 @@
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>9月29日に、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名を訂正した。報告書そのものの中の食い違い2件（回収数と集計の基数、通いの場の本文と図）は第4章に記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>小野町_地域分析・検討シート_記入案_20260930.xlsx／同_記入案_20260930.docx</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9月30日</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>9月30日にお送りいただいた地域分析・検討シートの自由記述欄（3ブロック×4欄）の記入案と、その根拠です。この欄は保険者機能強化推進交付金の評価指標（推進Ⅰ(ⅰ)1・同(ⅱ)）に直結します。数値はすべて受領シートから計算しており、固定値は書いていません</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3204,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（19件）</t>
+          <t>いただきたい資料（21件）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
